--- a/NAVIPACK_Order_Tool/NAVIPACK_Siparis_Hacim_Hesaplama.xlsx
+++ b/NAVIPACK_Order_Tool/NAVIPACK_Siparis_Hacim_Hesaplama.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +56,14 @@
     </font>
     <font>
       <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00833C00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00833C00"/>
     </font>
     <font>
       <b val="1"/>
@@ -128,6 +136,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00833C00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00BF8F00"/>
       </patternFill>
     </fill>
@@ -153,7 +166,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAFAFA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -173,12 +186,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00833C00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FBE9DD"/>
       </patternFill>
     </fill>
   </fills>
@@ -222,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -233,22 +241,22 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -260,7 +268,10 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -270,6 +281,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -285,84 +299,77 @@
     <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="15" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="15" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="15" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="15" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="3" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,9 +459,29 @@
 Dolum HACME gore hesaplanir.</t>
       </text>
     </comment>
-    <comment ref="K6" authorId="0" shapeId="0">
+    <comment ref="D6" authorId="0" shapeId="0">
       <text>
-        <t>Siparisi KOLI cinsinden girin. Her hucre sadece KOLI/SIRA katlarini kabul eder.</t>
+        <t>PALET = paletli yuklenir (tam sira zorunlu). DOKME = palet ustu dokme / bulk (serbest adet).</t>
+      </text>
+    </comment>
+    <comment ref="L6" authorId="0" shapeId="0">
+      <text>
+        <t>Siparisi KOLI cinsinden girin. PALET urunlerde sadece KOLI/SIRA katlari kabul edilir.</t>
+      </text>
+    </comment>
+    <comment ref="K27" authorId="0" shapeId="0">
+      <text>
+        <t>Bu urun NAVIPACK fiyat teklifinde YOK. FIYAT/1000 hucresini (K) elle giriniz.</t>
+      </text>
+    </comment>
+    <comment ref="K28" authorId="0" shapeId="0">
+      <text>
+        <t>Bu urun NAVIPACK fiyat teklifinde YOK. FIYAT/1000 hucresini (K) elle giriniz.</t>
+      </text>
+    </comment>
+    <comment ref="K29" authorId="0" shapeId="0">
+      <text>
+        <t>Bu urun NAVIPACK fiyat teklifinde YOK. FIYAT/1000 hucresini (K) elle giriniz.</t>
       </text>
     </comment>
   </commentList>
@@ -750,27 +777,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -778,7 +806,7 @@
         <is>
           <t>NAVIPACK LLC
 SIPARIS &amp; HACIM HESAPLAMA
-ORDER &amp; VOLUME CALCULATOR</t>
+ORDER &amp; VOLUME CALCULATOR (v3)</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -787,24 +815,24 @@
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr"/>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>TOPLAM
 HACIM m3</t>
         </is>
       </c>
-      <c r="M1" s="5">
-        <f>P27</f>
-        <v/>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="N1" s="5">
+        <f>Q30</f>
+        <v/>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>TIR
 DOLULUK %</t>
         </is>
       </c>
-      <c r="Q1" s="6">
-        <f>IF($G$3=0,0,P27/$G$3)</f>
+      <c r="R1" s="6">
+        <f>IF($G$3=0,0,Q30/$G$3)</f>
         <v/>
       </c>
     </row>
@@ -828,24 +856,24 @@
       <c r="G3" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>GEREKEN
 TIR ADEDI</t>
         </is>
       </c>
-      <c r="M3" s="8">
-        <f>IF($G$3=0,0,CEILING(P27/$G$3,1))</f>
-        <v/>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="N3" s="8">
+        <f>IF($G$3=0,0,CEILING(Q30/$G$3,1))</f>
+        <v/>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>TOPLAM
 TUTAR USD</t>
         </is>
       </c>
-      <c r="Q3" s="9">
-        <f>Q27</f>
+      <c r="R3" s="9">
+        <f>R30</f>
         <v/>
       </c>
     </row>
@@ -866,1553 +894,1873 @@
           <t>RENK / COLOUR</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>YUKLEME
+TIPI</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>ADET/KOLI
 (pcs/box)</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>KOLI HACMI
 m3</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>KOLI NET
 kg</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>KOLI/SIRA
 (box/layer)</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>SIRA/PALET
 (layer/pal)</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>KOLI/PALET
 (box/pal)</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr">
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>FIYAT/1000
 USD</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>SIPARIS
 (KOLI) ***</t>
         </is>
       </c>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="M6" s="13" t="inlineStr">
         <is>
           <t>SIPARIS
 (ADET)</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t>PALET
 (esdeger)</t>
         </is>
       </c>
-      <c r="N6" s="12" t="inlineStr">
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t>TAM SIRA
 (rows)</t>
         </is>
       </c>
-      <c r="O6" s="12" t="inlineStr">
+      <c r="P6" s="13" t="inlineStr">
         <is>
           <t>NET AGIRLIK
 kg</t>
         </is>
       </c>
-      <c r="P6" s="12" t="inlineStr">
+      <c r="Q6" s="13" t="inlineStr">
         <is>
           <t>HACIM
 m3</t>
         </is>
       </c>
-      <c r="Q6" s="12" t="inlineStr">
+      <c r="R6" s="13" t="inlineStr">
         <is>
           <t>TUTAR
 USD</t>
         </is>
       </c>
-      <c r="R6" s="13" t="inlineStr">
-        <is>
-          <t>AILE / FAMILY</t>
+      <c r="S6" s="14" t="inlineStr">
+        <is>
+          <t>AILE</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="n">
+      <c r="A7" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>PREMIUM FORK</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>TRANSPARENT</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="F7" s="20" t="n">
         <v>0.046</v>
       </c>
-      <c r="F7" s="19">
-        <f>D7*2.8/1000</f>
-        <v/>
-      </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="21">
+        <f>E7*2.8/1000</f>
+        <v/>
+      </c>
+      <c r="H7" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I7" s="14">
-        <f>G7*H7</f>
-        <v/>
-      </c>
-      <c r="J7" s="20" t="n">
+      <c r="J7" s="15">
+        <f>IF(OR(H7="",I7=""),0,H7*I7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="22" t="n">
         <v>7.5</v>
       </c>
-      <c r="K7" s="21" t="n">
+      <c r="L7" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="22">
-        <f>K7*D7</f>
-        <v/>
-      </c>
-      <c r="M7" s="23">
-        <f>IF(I7=0,0,K7/I7)</f>
-        <v/>
-      </c>
-      <c r="N7" s="24">
-        <f>IF(G7=0,0,K7/G7)</f>
-        <v/>
-      </c>
-      <c r="O7" s="25">
-        <f>K7*F7</f>
-        <v/>
-      </c>
-      <c r="P7" s="26">
-        <f>K7*E7</f>
-        <v/>
-      </c>
-      <c r="Q7" s="27">
-        <f>L7/1000*J7</f>
-        <v/>
-      </c>
-      <c r="R7" s="28" t="inlineStr">
+      <c r="M7" s="24">
+        <f>L7*E7</f>
+        <v/>
+      </c>
+      <c r="N7" s="25">
+        <f>IF(D7="DOKME",0,IF(J7=0,0,L7/J7))</f>
+        <v/>
+      </c>
+      <c r="O7" s="26">
+        <f>IF(D7="DOKME",0,IF(H7=0,0,L7/H7))</f>
+        <v/>
+      </c>
+      <c r="P7" s="27">
+        <f>L7*G7</f>
+        <v/>
+      </c>
+      <c r="Q7" s="28">
+        <f>L7*F7</f>
+        <v/>
+      </c>
+      <c r="R7" s="29">
+        <f>IF(K7="",0,M7/1000*K7)</f>
+        <v/>
+      </c>
+      <c r="S7" s="30" t="inlineStr">
         <is>
           <t>PREMIUM</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="n">
+      <c r="A8" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>PREMIUM FORK</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>BLACK</t>
         </is>
       </c>
-      <c r="D8" s="32" t="n">
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="E8" s="33" t="n">
+      <c r="F8" s="20" t="n">
         <v>0.046</v>
       </c>
-      <c r="F8" s="34">
-        <f>D8*2.8/1000</f>
-        <v/>
-      </c>
-      <c r="G8" s="29" t="n">
+      <c r="G8" s="21">
+        <f>E8*2.8/1000</f>
+        <v/>
+      </c>
+      <c r="H8" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="H8" s="29" t="n">
+      <c r="I8" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I8" s="29">
-        <f>G8*H8</f>
-        <v/>
-      </c>
-      <c r="J8" s="35" t="n">
+      <c r="J8" s="15">
+        <f>IF(OR(H8="",I8=""),0,H8*I8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="22" t="n">
         <v>7.5</v>
       </c>
-      <c r="K8" s="21" t="n">
+      <c r="L8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="22">
-        <f>K8*D8</f>
-        <v/>
-      </c>
-      <c r="M8" s="23">
-        <f>IF(I8=0,0,K8/I8)</f>
-        <v/>
-      </c>
-      <c r="N8" s="24">
-        <f>IF(G8=0,0,K8/G8)</f>
-        <v/>
-      </c>
-      <c r="O8" s="25">
-        <f>K8*F8</f>
-        <v/>
-      </c>
-      <c r="P8" s="26">
-        <f>K8*E8</f>
-        <v/>
-      </c>
-      <c r="Q8" s="27">
-        <f>L8/1000*J8</f>
-        <v/>
-      </c>
-      <c r="R8" s="28" t="inlineStr">
+      <c r="M8" s="24">
+        <f>L8*E8</f>
+        <v/>
+      </c>
+      <c r="N8" s="25">
+        <f>IF(D8="DOKME",0,IF(J8=0,0,L8/J8))</f>
+        <v/>
+      </c>
+      <c r="O8" s="26">
+        <f>IF(D8="DOKME",0,IF(H8=0,0,L8/H8))</f>
+        <v/>
+      </c>
+      <c r="P8" s="27">
+        <f>L8*G8</f>
+        <v/>
+      </c>
+      <c r="Q8" s="28">
+        <f>L8*F8</f>
+        <v/>
+      </c>
+      <c r="R8" s="29">
+        <f>IF(K8="",0,M8/1000*K8)</f>
+        <v/>
+      </c>
+      <c r="S8" s="30" t="inlineStr">
         <is>
           <t>PREMIUM</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>PREMIUM SPOON</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>TRANSPARENT</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="F9" s="20" t="n">
         <v>0.056</v>
       </c>
-      <c r="F9" s="19">
-        <f>D9*2.8/1000</f>
-        <v/>
-      </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="21">
+        <f>E9*2.8/1000</f>
+        <v/>
+      </c>
+      <c r="H9" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="I9" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="I9" s="14">
-        <f>G9*H9</f>
-        <v/>
-      </c>
-      <c r="J9" s="20" t="n">
+      <c r="J9" s="15">
+        <f>IF(OR(H9="",I9=""),0,H9*I9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="22" t="n">
         <v>7.5</v>
       </c>
-      <c r="K9" s="21" t="n">
+      <c r="L9" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="22">
-        <f>K9*D9</f>
-        <v/>
-      </c>
-      <c r="M9" s="23">
-        <f>IF(I9=0,0,K9/I9)</f>
-        <v/>
-      </c>
-      <c r="N9" s="24">
-        <f>IF(G9=0,0,K9/G9)</f>
-        <v/>
-      </c>
-      <c r="O9" s="25">
-        <f>K9*F9</f>
-        <v/>
-      </c>
-      <c r="P9" s="26">
-        <f>K9*E9</f>
-        <v/>
-      </c>
-      <c r="Q9" s="27">
-        <f>L9/1000*J9</f>
-        <v/>
-      </c>
-      <c r="R9" s="28" t="inlineStr">
+      <c r="M9" s="24">
+        <f>L9*E9</f>
+        <v/>
+      </c>
+      <c r="N9" s="25">
+        <f>IF(D9="DOKME",0,IF(J9=0,0,L9/J9))</f>
+        <v/>
+      </c>
+      <c r="O9" s="26">
+        <f>IF(D9="DOKME",0,IF(H9=0,0,L9/H9))</f>
+        <v/>
+      </c>
+      <c r="P9" s="27">
+        <f>L9*G9</f>
+        <v/>
+      </c>
+      <c r="Q9" s="28">
+        <f>L9*F9</f>
+        <v/>
+      </c>
+      <c r="R9" s="29">
+        <f>IF(K9="",0,M9/1000*K9)</f>
+        <v/>
+      </c>
+      <c r="S9" s="30" t="inlineStr">
         <is>
           <t>PREMIUM</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="n">
+      <c r="A10" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>PREMIUM SPOON</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>BLACK</t>
         </is>
       </c>
-      <c r="D10" s="32" t="n">
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="F10" s="20" t="n">
         <v>0.056</v>
       </c>
-      <c r="F10" s="34">
-        <f>D10*2.8/1000</f>
-        <v/>
-      </c>
-      <c r="G10" s="29" t="n">
+      <c r="G10" s="21">
+        <f>E10*2.8/1000</f>
+        <v/>
+      </c>
+      <c r="H10" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="H10" s="29" t="n">
+      <c r="I10" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="I10" s="29">
-        <f>G10*H10</f>
-        <v/>
-      </c>
-      <c r="J10" s="35" t="n">
+      <c r="J10" s="15">
+        <f>IF(OR(H10="",I10=""),0,H10*I10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="22" t="n">
         <v>7.5</v>
       </c>
-      <c r="K10" s="21" t="n">
+      <c r="L10" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="22">
-        <f>K10*D10</f>
-        <v/>
-      </c>
-      <c r="M10" s="23">
-        <f>IF(I10=0,0,K10/I10)</f>
-        <v/>
-      </c>
-      <c r="N10" s="24">
-        <f>IF(G10=0,0,K10/G10)</f>
-        <v/>
-      </c>
-      <c r="O10" s="25">
-        <f>K10*F10</f>
-        <v/>
-      </c>
-      <c r="P10" s="26">
-        <f>K10*E10</f>
-        <v/>
-      </c>
-      <c r="Q10" s="27">
-        <f>L10/1000*J10</f>
-        <v/>
-      </c>
-      <c r="R10" s="28" t="inlineStr">
+      <c r="M10" s="24">
+        <f>L10*E10</f>
+        <v/>
+      </c>
+      <c r="N10" s="25">
+        <f>IF(D10="DOKME",0,IF(J10=0,0,L10/J10))</f>
+        <v/>
+      </c>
+      <c r="O10" s="26">
+        <f>IF(D10="DOKME",0,IF(H10=0,0,L10/H10))</f>
+        <v/>
+      </c>
+      <c r="P10" s="27">
+        <f>L10*G10</f>
+        <v/>
+      </c>
+      <c r="Q10" s="28">
+        <f>L10*F10</f>
+        <v/>
+      </c>
+      <c r="R10" s="29">
+        <f>IF(K10="",0,M10/1000*K10)</f>
+        <v/>
+      </c>
+      <c r="S10" s="30" t="inlineStr">
         <is>
           <t>PREMIUM</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>PREMIUM KNIFE</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>TRANSPARENT</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="F11" s="20" t="n">
         <v>0.035</v>
       </c>
-      <c r="F11" s="19">
-        <f>D11*2.8/1000</f>
-        <v/>
-      </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="21">
+        <f>E11*2.8/1000</f>
+        <v/>
+      </c>
+      <c r="H11" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="I11" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="I11" s="14">
-        <f>G11*H11</f>
-        <v/>
-      </c>
-      <c r="J11" s="20" t="n">
+      <c r="J11" s="15">
+        <f>IF(OR(H11="",I11=""),0,H11*I11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="22" t="n">
         <v>7.5</v>
       </c>
-      <c r="K11" s="21" t="n">
+      <c r="L11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="22">
-        <f>K11*D11</f>
-        <v/>
-      </c>
-      <c r="M11" s="23">
-        <f>IF(I11=0,0,K11/I11)</f>
-        <v/>
-      </c>
-      <c r="N11" s="24">
-        <f>IF(G11=0,0,K11/G11)</f>
-        <v/>
-      </c>
-      <c r="O11" s="25">
-        <f>K11*F11</f>
-        <v/>
-      </c>
-      <c r="P11" s="26">
-        <f>K11*E11</f>
-        <v/>
-      </c>
-      <c r="Q11" s="27">
-        <f>L11/1000*J11</f>
-        <v/>
-      </c>
-      <c r="R11" s="28" t="inlineStr">
+      <c r="M11" s="24">
+        <f>L11*E11</f>
+        <v/>
+      </c>
+      <c r="N11" s="25">
+        <f>IF(D11="DOKME",0,IF(J11=0,0,L11/J11))</f>
+        <v/>
+      </c>
+      <c r="O11" s="26">
+        <f>IF(D11="DOKME",0,IF(H11=0,0,L11/H11))</f>
+        <v/>
+      </c>
+      <c r="P11" s="27">
+        <f>L11*G11</f>
+        <v/>
+      </c>
+      <c r="Q11" s="28">
+        <f>L11*F11</f>
+        <v/>
+      </c>
+      <c r="R11" s="29">
+        <f>IF(K11="",0,M11/1000*K11)</f>
+        <v/>
+      </c>
+      <c r="S11" s="30" t="inlineStr">
         <is>
           <t>PREMIUM</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="n">
+      <c r="A12" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>PREMIUM KNIFE</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>BLACK</t>
         </is>
       </c>
-      <c r="D12" s="32" t="n">
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="F12" s="20" t="n">
         <v>0.035</v>
       </c>
-      <c r="F12" s="34">
-        <f>D12*2.8/1000</f>
-        <v/>
-      </c>
-      <c r="G12" s="29" t="n">
+      <c r="G12" s="21">
+        <f>E12*2.8/1000</f>
+        <v/>
+      </c>
+      <c r="H12" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="H12" s="29" t="n">
+      <c r="I12" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="I12" s="29">
-        <f>G12*H12</f>
-        <v/>
-      </c>
-      <c r="J12" s="35" t="n">
+      <c r="J12" s="15">
+        <f>IF(OR(H12="",I12=""),0,H12*I12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="22" t="n">
         <v>7.5</v>
       </c>
-      <c r="K12" s="21" t="n">
+      <c r="L12" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="22">
-        <f>K12*D12</f>
-        <v/>
-      </c>
-      <c r="M12" s="23">
-        <f>IF(I12=0,0,K12/I12)</f>
-        <v/>
-      </c>
-      <c r="N12" s="24">
-        <f>IF(G12=0,0,K12/G12)</f>
-        <v/>
-      </c>
-      <c r="O12" s="25">
-        <f>K12*F12</f>
-        <v/>
-      </c>
-      <c r="P12" s="26">
-        <f>K12*E12</f>
-        <v/>
-      </c>
-      <c r="Q12" s="27">
-        <f>L12/1000*J12</f>
-        <v/>
-      </c>
-      <c r="R12" s="28" t="inlineStr">
+      <c r="M12" s="24">
+        <f>L12*E12</f>
+        <v/>
+      </c>
+      <c r="N12" s="25">
+        <f>IF(D12="DOKME",0,IF(J12=0,0,L12/J12))</f>
+        <v/>
+      </c>
+      <c r="O12" s="26">
+        <f>IF(D12="DOKME",0,IF(H12=0,0,L12/H12))</f>
+        <v/>
+      </c>
+      <c r="P12" s="27">
+        <f>L12*G12</f>
+        <v/>
+      </c>
+      <c r="Q12" s="28">
+        <f>L12*F12</f>
+        <v/>
+      </c>
+      <c r="R12" s="29">
+        <f>IF(K12="",0,M12/1000*K12)</f>
+        <v/>
+      </c>
+      <c r="S12" s="30" t="inlineStr">
         <is>
           <t>PREMIUM</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>PREMIUM DESSERT SPOON</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>TRANSPARENT</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="F13" s="20" t="n">
         <v>0.036</v>
       </c>
-      <c r="F13" s="19">
-        <f>D13*2.5/1000</f>
-        <v/>
-      </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="21">
+        <f>E13*2.5/1000</f>
+        <v/>
+      </c>
+      <c r="H13" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="I13" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="I13" s="14">
-        <f>G13*H13</f>
-        <v/>
-      </c>
-      <c r="J13" s="20" t="n">
+      <c r="J13" s="15">
+        <f>IF(OR(H13="",I13=""),0,H13*I13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="22" t="n">
         <v>7.25</v>
       </c>
-      <c r="K13" s="21" t="n">
+      <c r="L13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="22">
-        <f>K13*D13</f>
-        <v/>
-      </c>
-      <c r="M13" s="23">
-        <f>IF(I13=0,0,K13/I13)</f>
-        <v/>
-      </c>
-      <c r="N13" s="24">
-        <f>IF(G13=0,0,K13/G13)</f>
-        <v/>
-      </c>
-      <c r="O13" s="25">
-        <f>K13*F13</f>
-        <v/>
-      </c>
-      <c r="P13" s="26">
-        <f>K13*E13</f>
-        <v/>
-      </c>
-      <c r="Q13" s="27">
-        <f>L13/1000*J13</f>
-        <v/>
-      </c>
-      <c r="R13" s="28" t="inlineStr">
+      <c r="M13" s="24">
+        <f>L13*E13</f>
+        <v/>
+      </c>
+      <c r="N13" s="25">
+        <f>IF(D13="DOKME",0,IF(J13=0,0,L13/J13))</f>
+        <v/>
+      </c>
+      <c r="O13" s="26">
+        <f>IF(D13="DOKME",0,IF(H13=0,0,L13/H13))</f>
+        <v/>
+      </c>
+      <c r="P13" s="27">
+        <f>L13*G13</f>
+        <v/>
+      </c>
+      <c r="Q13" s="28">
+        <f>L13*F13</f>
+        <v/>
+      </c>
+      <c r="R13" s="29">
+        <f>IF(K13="",0,M13/1000*K13)</f>
+        <v/>
+      </c>
+      <c r="S13" s="30" t="inlineStr">
         <is>
           <t>PREMIUM</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="n">
+      <c r="A14" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>PREMIUM DESSERT SPOON</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>BLACK</t>
         </is>
       </c>
-      <c r="D14" s="32" t="n">
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="F14" s="20" t="n">
         <v>0.036</v>
       </c>
-      <c r="F14" s="34">
-        <f>D14*2.5/1000</f>
-        <v/>
-      </c>
-      <c r="G14" s="29" t="n">
+      <c r="G14" s="21">
+        <f>E14*2.5/1000</f>
+        <v/>
+      </c>
+      <c r="H14" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="29" t="n">
+      <c r="I14" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="I14" s="29">
-        <f>G14*H14</f>
-        <v/>
-      </c>
-      <c r="J14" s="35" t="n">
+      <c r="J14" s="15">
+        <f>IF(OR(H14="",I14=""),0,H14*I14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="22" t="n">
         <v>7.25</v>
       </c>
-      <c r="K14" s="21" t="n">
+      <c r="L14" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="22">
-        <f>K14*D14</f>
-        <v/>
-      </c>
-      <c r="M14" s="23">
-        <f>IF(I14=0,0,K14/I14)</f>
-        <v/>
-      </c>
-      <c r="N14" s="24">
-        <f>IF(G14=0,0,K14/G14)</f>
-        <v/>
-      </c>
-      <c r="O14" s="25">
-        <f>K14*F14</f>
-        <v/>
-      </c>
-      <c r="P14" s="26">
-        <f>K14*E14</f>
-        <v/>
-      </c>
-      <c r="Q14" s="27">
-        <f>L14/1000*J14</f>
-        <v/>
-      </c>
-      <c r="R14" s="28" t="inlineStr">
+      <c r="M14" s="24">
+        <f>L14*E14</f>
+        <v/>
+      </c>
+      <c r="N14" s="25">
+        <f>IF(D14="DOKME",0,IF(J14=0,0,L14/J14))</f>
+        <v/>
+      </c>
+      <c r="O14" s="26">
+        <f>IF(D14="DOKME",0,IF(H14=0,0,L14/H14))</f>
+        <v/>
+      </c>
+      <c r="P14" s="27">
+        <f>L14*G14</f>
+        <v/>
+      </c>
+      <c r="Q14" s="28">
+        <f>L14*F14</f>
+        <v/>
+      </c>
+      <c r="R14" s="29">
+        <f>IF(K14="",0,M14/1000*K14)</f>
+        <v/>
+      </c>
+      <c r="S14" s="30" t="inlineStr">
         <is>
           <t>PREMIUM</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n">
+      <c r="A15" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>DIAMOND FORK</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>TRANSPARENT</t>
         </is>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="n">
         <v>2000</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="F15" s="20" t="n">
         <v>0.024</v>
       </c>
-      <c r="F15" s="19">
-        <f>D15*3.8/1000</f>
-        <v/>
-      </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="21">
+        <f>E15*3.8/1000</f>
+        <v/>
+      </c>
+      <c r="H15" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="I15" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I15" s="14">
-        <f>G15*H15</f>
-        <v/>
-      </c>
-      <c r="J15" s="20" t="n">
+      <c r="J15" s="15">
+        <f>IF(OR(H15="",I15=""),0,H15*I15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="K15" s="21" t="n">
+      <c r="L15" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="22">
-        <f>K15*D15</f>
-        <v/>
-      </c>
-      <c r="M15" s="23">
-        <f>IF(I15=0,0,K15/I15)</f>
-        <v/>
-      </c>
-      <c r="N15" s="24">
-        <f>IF(G15=0,0,K15/G15)</f>
-        <v/>
-      </c>
-      <c r="O15" s="25">
-        <f>K15*F15</f>
-        <v/>
-      </c>
-      <c r="P15" s="26">
-        <f>K15*E15</f>
-        <v/>
-      </c>
-      <c r="Q15" s="27">
-        <f>L15/1000*J15</f>
-        <v/>
-      </c>
-      <c r="R15" s="28" t="inlineStr">
+      <c r="M15" s="24">
+        <f>L15*E15</f>
+        <v/>
+      </c>
+      <c r="N15" s="25">
+        <f>IF(D15="DOKME",0,IF(J15=0,0,L15/J15))</f>
+        <v/>
+      </c>
+      <c r="O15" s="26">
+        <f>IF(D15="DOKME",0,IF(H15=0,0,L15/H15))</f>
+        <v/>
+      </c>
+      <c r="P15" s="27">
+        <f>L15*G15</f>
+        <v/>
+      </c>
+      <c r="Q15" s="28">
+        <f>L15*F15</f>
+        <v/>
+      </c>
+      <c r="R15" s="29">
+        <f>IF(K15="",0,M15/1000*K15)</f>
+        <v/>
+      </c>
+      <c r="S15" s="30" t="inlineStr">
         <is>
           <t>DIAMOND</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="n">
+      <c r="A16" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>DIAMOND FORK</t>
         </is>
       </c>
-      <c r="C16" s="31" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>BLACK</t>
         </is>
       </c>
-      <c r="D16" s="32" t="n">
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="n">
         <v>2000</v>
       </c>
-      <c r="E16" s="33" t="n">
+      <c r="F16" s="20" t="n">
         <v>0.024</v>
       </c>
-      <c r="F16" s="34">
-        <f>D16*3.8/1000</f>
-        <v/>
-      </c>
-      <c r="G16" s="29" t="n">
+      <c r="G16" s="21">
+        <f>E16*3.8/1000</f>
+        <v/>
+      </c>
+      <c r="H16" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="H16" s="29" t="n">
+      <c r="I16" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I16" s="29">
-        <f>G16*H16</f>
-        <v/>
-      </c>
-      <c r="J16" s="35" t="n">
+      <c r="J16" s="15">
+        <f>IF(OR(H16="",I16=""),0,H16*I16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="K16" s="21" t="n">
+      <c r="L16" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="22">
-        <f>K16*D16</f>
-        <v/>
-      </c>
-      <c r="M16" s="23">
-        <f>IF(I16=0,0,K16/I16)</f>
-        <v/>
-      </c>
-      <c r="N16" s="24">
-        <f>IF(G16=0,0,K16/G16)</f>
-        <v/>
-      </c>
-      <c r="O16" s="25">
-        <f>K16*F16</f>
-        <v/>
-      </c>
-      <c r="P16" s="26">
-        <f>K16*E16</f>
-        <v/>
-      </c>
-      <c r="Q16" s="27">
-        <f>L16/1000*J16</f>
-        <v/>
-      </c>
-      <c r="R16" s="28" t="inlineStr">
+      <c r="M16" s="24">
+        <f>L16*E16</f>
+        <v/>
+      </c>
+      <c r="N16" s="25">
+        <f>IF(D16="DOKME",0,IF(J16=0,0,L16/J16))</f>
+        <v/>
+      </c>
+      <c r="O16" s="26">
+        <f>IF(D16="DOKME",0,IF(H16=0,0,L16/H16))</f>
+        <v/>
+      </c>
+      <c r="P16" s="27">
+        <f>L16*G16</f>
+        <v/>
+      </c>
+      <c r="Q16" s="28">
+        <f>L16*F16</f>
+        <v/>
+      </c>
+      <c r="R16" s="29">
+        <f>IF(K16="",0,M16/1000*K16)</f>
+        <v/>
+      </c>
+      <c r="S16" s="30" t="inlineStr">
         <is>
           <t>DIAMOND</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>DIAMOND SPOON</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>TRANSPARENT</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="n">
         <v>2000</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="F17" s="20" t="n">
         <v>0.031</v>
       </c>
-      <c r="F17" s="19">
-        <f>D17*3.8/1000</f>
-        <v/>
-      </c>
-      <c r="G17" s="14" t="n">
+      <c r="G17" s="21">
+        <f>E17*3.8/1000</f>
+        <v/>
+      </c>
+      <c r="H17" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="H17" s="14" t="n">
+      <c r="I17" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="I17" s="14">
-        <f>G17*H17</f>
-        <v/>
-      </c>
-      <c r="J17" s="20" t="n">
+      <c r="J17" s="15">
+        <f>IF(OR(H17="",I17=""),0,H17*I17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="K17" s="21" t="n">
+      <c r="L17" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="22">
-        <f>K17*D17</f>
-        <v/>
-      </c>
-      <c r="M17" s="23">
-        <f>IF(I17=0,0,K17/I17)</f>
-        <v/>
-      </c>
-      <c r="N17" s="24">
-        <f>IF(G17=0,0,K17/G17)</f>
-        <v/>
-      </c>
-      <c r="O17" s="25">
-        <f>K17*F17</f>
-        <v/>
-      </c>
-      <c r="P17" s="26">
-        <f>K17*E17</f>
-        <v/>
-      </c>
-      <c r="Q17" s="27">
-        <f>L17/1000*J17</f>
-        <v/>
-      </c>
-      <c r="R17" s="28" t="inlineStr">
+      <c r="M17" s="24">
+        <f>L17*E17</f>
+        <v/>
+      </c>
+      <c r="N17" s="25">
+        <f>IF(D17="DOKME",0,IF(J17=0,0,L17/J17))</f>
+        <v/>
+      </c>
+      <c r="O17" s="26">
+        <f>IF(D17="DOKME",0,IF(H17=0,0,L17/H17))</f>
+        <v/>
+      </c>
+      <c r="P17" s="27">
+        <f>L17*G17</f>
+        <v/>
+      </c>
+      <c r="Q17" s="28">
+        <f>L17*F17</f>
+        <v/>
+      </c>
+      <c r="R17" s="29">
+        <f>IF(K17="",0,M17/1000*K17)</f>
+        <v/>
+      </c>
+      <c r="S17" s="30" t="inlineStr">
         <is>
           <t>DIAMOND</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="n">
+      <c r="A18" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>DIAMOND SPOON</t>
         </is>
       </c>
-      <c r="C18" s="31" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>BLACK</t>
         </is>
       </c>
-      <c r="D18" s="32" t="n">
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="n">
         <v>2000</v>
       </c>
-      <c r="E18" s="33" t="n">
+      <c r="F18" s="20" t="n">
         <v>0.031</v>
       </c>
-      <c r="F18" s="34">
-        <f>D18*3.8/1000</f>
-        <v/>
-      </c>
-      <c r="G18" s="29" t="n">
+      <c r="G18" s="21">
+        <f>E18*3.8/1000</f>
+        <v/>
+      </c>
+      <c r="H18" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="H18" s="29" t="n">
+      <c r="I18" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="I18" s="29">
-        <f>G18*H18</f>
-        <v/>
-      </c>
-      <c r="J18" s="35" t="n">
+      <c r="J18" s="15">
+        <f>IF(OR(H18="",I18=""),0,H18*I18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="K18" s="21" t="n">
+      <c r="L18" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="22">
-        <f>K18*D18</f>
-        <v/>
-      </c>
-      <c r="M18" s="23">
-        <f>IF(I18=0,0,K18/I18)</f>
-        <v/>
-      </c>
-      <c r="N18" s="24">
-        <f>IF(G18=0,0,K18/G18)</f>
-        <v/>
-      </c>
-      <c r="O18" s="25">
-        <f>K18*F18</f>
-        <v/>
-      </c>
-      <c r="P18" s="26">
-        <f>K18*E18</f>
-        <v/>
-      </c>
-      <c r="Q18" s="27">
-        <f>L18/1000*J18</f>
-        <v/>
-      </c>
-      <c r="R18" s="28" t="inlineStr">
+      <c r="M18" s="24">
+        <f>L18*E18</f>
+        <v/>
+      </c>
+      <c r="N18" s="25">
+        <f>IF(D18="DOKME",0,IF(J18=0,0,L18/J18))</f>
+        <v/>
+      </c>
+      <c r="O18" s="26">
+        <f>IF(D18="DOKME",0,IF(H18=0,0,L18/H18))</f>
+        <v/>
+      </c>
+      <c r="P18" s="27">
+        <f>L18*G18</f>
+        <v/>
+      </c>
+      <c r="Q18" s="28">
+        <f>L18*F18</f>
+        <v/>
+      </c>
+      <c r="R18" s="29">
+        <f>IF(K18="",0,M18/1000*K18)</f>
+        <v/>
+      </c>
+      <c r="S18" s="30" t="inlineStr">
         <is>
           <t>DIAMOND</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>DIAMOND KNIFE</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>TRANSPARENT</t>
         </is>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="n">
         <v>2000</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="F19" s="20" t="n">
         <v>0.02</v>
       </c>
-      <c r="F19" s="19">
-        <f>D19*3.8/1000</f>
-        <v/>
-      </c>
-      <c r="G19" s="14" t="n">
+      <c r="G19" s="21">
+        <f>E19*3.8/1000</f>
+        <v/>
+      </c>
+      <c r="H19" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="H19" s="14" t="n">
+      <c r="I19" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="I19" s="14">
-        <f>G19*H19</f>
-        <v/>
-      </c>
-      <c r="J19" s="20" t="n">
+      <c r="J19" s="15">
+        <f>IF(OR(H19="",I19=""),0,H19*I19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="K19" s="21" t="n">
+      <c r="L19" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="22">
-        <f>K19*D19</f>
-        <v/>
-      </c>
-      <c r="M19" s="23">
-        <f>IF(I19=0,0,K19/I19)</f>
-        <v/>
-      </c>
-      <c r="N19" s="24">
-        <f>IF(G19=0,0,K19/G19)</f>
-        <v/>
-      </c>
-      <c r="O19" s="25">
-        <f>K19*F19</f>
-        <v/>
-      </c>
-      <c r="P19" s="26">
-        <f>K19*E19</f>
-        <v/>
-      </c>
-      <c r="Q19" s="27">
-        <f>L19/1000*J19</f>
-        <v/>
-      </c>
-      <c r="R19" s="28" t="inlineStr">
+      <c r="M19" s="24">
+        <f>L19*E19</f>
+        <v/>
+      </c>
+      <c r="N19" s="25">
+        <f>IF(D19="DOKME",0,IF(J19=0,0,L19/J19))</f>
+        <v/>
+      </c>
+      <c r="O19" s="26">
+        <f>IF(D19="DOKME",0,IF(H19=0,0,L19/H19))</f>
+        <v/>
+      </c>
+      <c r="P19" s="27">
+        <f>L19*G19</f>
+        <v/>
+      </c>
+      <c r="Q19" s="28">
+        <f>L19*F19</f>
+        <v/>
+      </c>
+      <c r="R19" s="29">
+        <f>IF(K19="",0,M19/1000*K19)</f>
+        <v/>
+      </c>
+      <c r="S19" s="30" t="inlineStr">
         <is>
           <t>DIAMOND</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="n">
+      <c r="A20" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>DIAMOND KNIFE</t>
         </is>
       </c>
-      <c r="C20" s="31" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>BLACK</t>
         </is>
       </c>
-      <c r="D20" s="32" t="n">
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="n">
         <v>2000</v>
       </c>
-      <c r="E20" s="33" t="n">
+      <c r="F20" s="20" t="n">
         <v>0.02</v>
       </c>
-      <c r="F20" s="34">
-        <f>D20*3.8/1000</f>
-        <v/>
-      </c>
-      <c r="G20" s="29" t="n">
+      <c r="G20" s="21">
+        <f>E20*3.8/1000</f>
+        <v/>
+      </c>
+      <c r="H20" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="H20" s="29" t="n">
+      <c r="I20" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="I20" s="29">
-        <f>G20*H20</f>
-        <v/>
-      </c>
-      <c r="J20" s="35" t="n">
+      <c r="J20" s="15">
+        <f>IF(OR(H20="",I20=""),0,H20*I20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="K20" s="21" t="n">
+      <c r="L20" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="22">
-        <f>K20*D20</f>
-        <v/>
-      </c>
-      <c r="M20" s="23">
-        <f>IF(I20=0,0,K20/I20)</f>
-        <v/>
-      </c>
-      <c r="N20" s="24">
-        <f>IF(G20=0,0,K20/G20)</f>
-        <v/>
-      </c>
-      <c r="O20" s="25">
-        <f>K20*F20</f>
-        <v/>
-      </c>
-      <c r="P20" s="26">
-        <f>K20*E20</f>
-        <v/>
-      </c>
-      <c r="Q20" s="27">
-        <f>L20/1000*J20</f>
-        <v/>
-      </c>
-      <c r="R20" s="28" t="inlineStr">
+      <c r="M20" s="24">
+        <f>L20*E20</f>
+        <v/>
+      </c>
+      <c r="N20" s="25">
+        <f>IF(D20="DOKME",0,IF(J20=0,0,L20/J20))</f>
+        <v/>
+      </c>
+      <c r="O20" s="26">
+        <f>IF(D20="DOKME",0,IF(H20=0,0,L20/H20))</f>
+        <v/>
+      </c>
+      <c r="P20" s="27">
+        <f>L20*G20</f>
+        <v/>
+      </c>
+      <c r="Q20" s="28">
+        <f>L20*F20</f>
+        <v/>
+      </c>
+      <c r="R20" s="29">
+        <f>IF(K20="",0,M20/1000*K20)</f>
+        <v/>
+      </c>
+      <c r="S20" s="30" t="inlineStr">
         <is>
           <t>DIAMOND</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>SMART FORK</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>TRANSPARENT / BLACK</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="n">
         <v>2000</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="F21" s="20" t="n">
         <v>0.025</v>
       </c>
-      <c r="F21" s="19">
-        <f>D21*3.7/1000</f>
-        <v/>
-      </c>
-      <c r="G21" s="14" t="n">
+      <c r="G21" s="21">
+        <f>E21*3.7/1000</f>
+        <v/>
+      </c>
+      <c r="H21" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="H21" s="14" t="n">
+      <c r="I21" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I21" s="14">
-        <f>G21*H21</f>
-        <v/>
-      </c>
-      <c r="J21" s="20" t="n">
+      <c r="J21" s="15">
+        <f>IF(OR(H21="",I21=""),0,H21*I21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="22" t="n">
         <v>9.75</v>
       </c>
-      <c r="K21" s="21" t="n">
+      <c r="L21" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="22">
-        <f>K21*D21</f>
-        <v/>
-      </c>
-      <c r="M21" s="23">
-        <f>IF(I21=0,0,K21/I21)</f>
-        <v/>
-      </c>
-      <c r="N21" s="24">
-        <f>IF(G21=0,0,K21/G21)</f>
-        <v/>
-      </c>
-      <c r="O21" s="25">
-        <f>K21*F21</f>
-        <v/>
-      </c>
-      <c r="P21" s="26">
-        <f>K21*E21</f>
-        <v/>
-      </c>
-      <c r="Q21" s="27">
-        <f>L21/1000*J21</f>
-        <v/>
-      </c>
-      <c r="R21" s="28" t="inlineStr">
+      <c r="M21" s="24">
+        <f>L21*E21</f>
+        <v/>
+      </c>
+      <c r="N21" s="25">
+        <f>IF(D21="DOKME",0,IF(J21=0,0,L21/J21))</f>
+        <v/>
+      </c>
+      <c r="O21" s="26">
+        <f>IF(D21="DOKME",0,IF(H21=0,0,L21/H21))</f>
+        <v/>
+      </c>
+      <c r="P21" s="27">
+        <f>L21*G21</f>
+        <v/>
+      </c>
+      <c r="Q21" s="28">
+        <f>L21*F21</f>
+        <v/>
+      </c>
+      <c r="R21" s="29">
+        <f>IF(K21="",0,M21/1000*K21)</f>
+        <v/>
+      </c>
+      <c r="S21" s="30" t="inlineStr">
         <is>
           <t>SMART</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="n">
+      <c r="A22" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>WAVY ICE CREAM SPOON</t>
         </is>
       </c>
-      <c r="C22" s="31" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>COLORED (RED/BLUE/GREEN/ORANGE)</t>
         </is>
       </c>
-      <c r="D22" s="32" t="n">
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="n">
         <v>2000</v>
       </c>
-      <c r="E22" s="33" t="n">
+      <c r="F22" s="20" t="n">
         <v>0.025</v>
       </c>
-      <c r="F22" s="34">
-        <f>D22*2.4/1000</f>
-        <v/>
-      </c>
-      <c r="G22" s="29" t="n">
+      <c r="G22" s="21">
+        <f>E22*2.4/1000</f>
+        <v/>
+      </c>
+      <c r="H22" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="H22" s="29" t="n">
+      <c r="I22" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="I22" s="29">
-        <f>G22*H22</f>
-        <v/>
-      </c>
-      <c r="J22" s="35" t="n">
+      <c r="J22" s="15">
+        <f>IF(OR(H22="",I22=""),0,H22*I22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="22" t="n">
         <v>8.5</v>
       </c>
-      <c r="K22" s="21" t="n">
+      <c r="L22" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="22">
-        <f>K22*D22</f>
-        <v/>
-      </c>
-      <c r="M22" s="23">
-        <f>IF(I22=0,0,K22/I22)</f>
-        <v/>
-      </c>
-      <c r="N22" s="24">
-        <f>IF(G22=0,0,K22/G22)</f>
-        <v/>
-      </c>
-      <c r="O22" s="25">
-        <f>K22*F22</f>
-        <v/>
-      </c>
-      <c r="P22" s="26">
-        <f>K22*E22</f>
-        <v/>
-      </c>
-      <c r="Q22" s="27">
-        <f>L22/1000*J22</f>
-        <v/>
-      </c>
-      <c r="R22" s="28" t="inlineStr">
+      <c r="M22" s="24">
+        <f>L22*E22</f>
+        <v/>
+      </c>
+      <c r="N22" s="25">
+        <f>IF(D22="DOKME",0,IF(J22=0,0,L22/J22))</f>
+        <v/>
+      </c>
+      <c r="O22" s="26">
+        <f>IF(D22="DOKME",0,IF(H22=0,0,L22/H22))</f>
+        <v/>
+      </c>
+      <c r="P22" s="27">
+        <f>L22*G22</f>
+        <v/>
+      </c>
+      <c r="Q22" s="28">
+        <f>L22*F22</f>
+        <v/>
+      </c>
+      <c r="R22" s="29">
+        <f>IF(K22="",0,M22/1000*K22)</f>
+        <v/>
+      </c>
+      <c r="S22" s="30" t="inlineStr">
         <is>
           <t>ICE CREAM</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>120 CC CHAMPAGNE GLASS</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>TRANSPARENT (FOOT COLORED)</t>
         </is>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="F23" s="20" t="n">
         <v>0.053</v>
       </c>
-      <c r="F23" s="19">
-        <f>D23*12.5/1000</f>
-        <v/>
-      </c>
-      <c r="G23" s="14" t="n">
+      <c r="G23" s="21">
+        <f>E23*12.5/1000</f>
+        <v/>
+      </c>
+      <c r="H23" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="H23" s="14" t="n">
+      <c r="I23" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="I23" s="14">
-        <f>G23*H23</f>
-        <v/>
-      </c>
-      <c r="J23" s="20" t="n">
+      <c r="J23" s="15">
+        <f>IF(OR(H23="",I23=""),0,H23*I23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="K23" s="21" t="n">
+      <c r="L23" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="22">
-        <f>K23*D23</f>
-        <v/>
-      </c>
-      <c r="M23" s="23">
-        <f>IF(I23=0,0,K23/I23)</f>
-        <v/>
-      </c>
-      <c r="N23" s="24">
-        <f>IF(G23=0,0,K23/G23)</f>
-        <v/>
-      </c>
-      <c r="O23" s="25">
-        <f>K23*F23</f>
-        <v/>
-      </c>
-      <c r="P23" s="26">
-        <f>K23*E23</f>
-        <v/>
-      </c>
-      <c r="Q23" s="27">
-        <f>L23/1000*J23</f>
-        <v/>
-      </c>
-      <c r="R23" s="28" t="inlineStr">
+      <c r="M23" s="24">
+        <f>L23*E23</f>
+        <v/>
+      </c>
+      <c r="N23" s="25">
+        <f>IF(D23="DOKME",0,IF(J23=0,0,L23/J23))</f>
+        <v/>
+      </c>
+      <c r="O23" s="26">
+        <f>IF(D23="DOKME",0,IF(H23=0,0,L23/H23))</f>
+        <v/>
+      </c>
+      <c r="P23" s="27">
+        <f>L23*G23</f>
+        <v/>
+      </c>
+      <c r="Q23" s="28">
+        <f>L23*F23</f>
+        <v/>
+      </c>
+      <c r="R23" s="29">
+        <f>IF(K23="",0,M23/1000*K23)</f>
+        <v/>
+      </c>
+      <c r="S23" s="30" t="inlineStr">
         <is>
           <t>GLASS</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="n">
+      <c r="A24" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>170 CC MINI WINE GLASS</t>
         </is>
       </c>
-      <c r="C24" s="31" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>TRANSPARENT (FOOT COLORED)</t>
         </is>
       </c>
-      <c r="D24" s="32" t="n">
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="E24" s="33" t="n">
+      <c r="F24" s="20" t="n">
         <v>0.049</v>
       </c>
-      <c r="F24" s="34">
-        <f>D24*12.5/1000</f>
-        <v/>
-      </c>
-      <c r="G24" s="29" t="n">
+      <c r="G24" s="21">
+        <f>E24*12.5/1000</f>
+        <v/>
+      </c>
+      <c r="H24" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="H24" s="29" t="n">
+      <c r="I24" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I24" s="29">
-        <f>G24*H24</f>
-        <v/>
-      </c>
-      <c r="J24" s="35" t="n">
+      <c r="J24" s="15">
+        <f>IF(OR(H24="",I24=""),0,H24*I24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="K24" s="21" t="n">
+      <c r="L24" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="22">
-        <f>K24*D24</f>
-        <v/>
-      </c>
-      <c r="M24" s="23">
-        <f>IF(I24=0,0,K24/I24)</f>
-        <v/>
-      </c>
-      <c r="N24" s="24">
-        <f>IF(G24=0,0,K24/G24)</f>
-        <v/>
-      </c>
-      <c r="O24" s="25">
-        <f>K24*F24</f>
-        <v/>
-      </c>
-      <c r="P24" s="26">
-        <f>K24*E24</f>
-        <v/>
-      </c>
-      <c r="Q24" s="27">
-        <f>L24/1000*J24</f>
-        <v/>
-      </c>
-      <c r="R24" s="28" t="inlineStr">
+      <c r="M24" s="24">
+        <f>L24*E24</f>
+        <v/>
+      </c>
+      <c r="N24" s="25">
+        <f>IF(D24="DOKME",0,IF(J24=0,0,L24/J24))</f>
+        <v/>
+      </c>
+      <c r="O24" s="26">
+        <f>IF(D24="DOKME",0,IF(H24=0,0,L24/H24))</f>
+        <v/>
+      </c>
+      <c r="P24" s="27">
+        <f>L24*G24</f>
+        <v/>
+      </c>
+      <c r="Q24" s="28">
+        <f>L24*F24</f>
+        <v/>
+      </c>
+      <c r="R24" s="29">
+        <f>IF(K24="",0,M24/1000*K24)</f>
+        <v/>
+      </c>
+      <c r="S24" s="30" t="inlineStr">
         <is>
           <t>GLASS</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>185 CC WINE GLASS</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>TRANSPARENT (FOOT COLORED)</t>
         </is>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="F25" s="20" t="n">
         <v>0.067</v>
       </c>
-      <c r="F25" s="19">
-        <f>D25*14.5/1000</f>
-        <v/>
-      </c>
-      <c r="G25" s="14" t="n">
+      <c r="G25" s="21">
+        <f>E25*14.5/1000</f>
+        <v/>
+      </c>
+      <c r="H25" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="H25" s="14" t="n">
+      <c r="I25" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="I25" s="14">
-        <f>G25*H25</f>
-        <v/>
-      </c>
-      <c r="J25" s="20" t="n">
+      <c r="J25" s="15">
+        <f>IF(OR(H25="",I25=""),0,H25*I25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="22" t="n">
         <v>110</v>
       </c>
-      <c r="K25" s="21" t="n">
+      <c r="L25" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="22">
-        <f>K25*D25</f>
-        <v/>
-      </c>
-      <c r="M25" s="23">
-        <f>IF(I25=0,0,K25/I25)</f>
-        <v/>
-      </c>
-      <c r="N25" s="24">
-        <f>IF(G25=0,0,K25/G25)</f>
-        <v/>
-      </c>
-      <c r="O25" s="25">
-        <f>K25*F25</f>
-        <v/>
-      </c>
-      <c r="P25" s="26">
-        <f>K25*E25</f>
-        <v/>
-      </c>
-      <c r="Q25" s="27">
-        <f>L25/1000*J25</f>
-        <v/>
-      </c>
-      <c r="R25" s="28" t="inlineStr">
+      <c r="M25" s="24">
+        <f>L25*E25</f>
+        <v/>
+      </c>
+      <c r="N25" s="25">
+        <f>IF(D25="DOKME",0,IF(J25=0,0,L25/J25))</f>
+        <v/>
+      </c>
+      <c r="O25" s="26">
+        <f>IF(D25="DOKME",0,IF(H25=0,0,L25/H25))</f>
+        <v/>
+      </c>
+      <c r="P25" s="27">
+        <f>L25*G25</f>
+        <v/>
+      </c>
+      <c r="Q25" s="28">
+        <f>L25*F25</f>
+        <v/>
+      </c>
+      <c r="R25" s="29">
+        <f>IF(K25="",0,M25/1000*K25)</f>
+        <v/>
+      </c>
+      <c r="S25" s="30" t="inlineStr">
         <is>
           <t>GLASS</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="n">
+      <c r="A26" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>PIZZA TRIPOD</t>
         </is>
       </c>
-      <c r="C26" s="31" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>WHITE</t>
         </is>
       </c>
-      <c r="D26" s="32" t="n">
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="n">
         <v>1000</v>
       </c>
-      <c r="E26" s="33" t="n">
+      <c r="F26" s="20" t="n">
         <v>0.027</v>
       </c>
-      <c r="F26" s="34">
-        <f>D26*1.85/1000</f>
-        <v/>
-      </c>
-      <c r="G26" s="29" t="n">
+      <c r="G26" s="21">
+        <f>E26*1.85/1000</f>
+        <v/>
+      </c>
+      <c r="H26" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="H26" s="29" t="n">
+      <c r="I26" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="I26" s="29">
-        <f>G26*H26</f>
-        <v/>
-      </c>
-      <c r="J26" s="35" t="n">
+      <c r="J26" s="15">
+        <f>IF(OR(H26="",I26=""),0,H26*I26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="22" t="n">
         <v>8.5</v>
       </c>
-      <c r="K26" s="21" t="n">
+      <c r="L26" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="22">
-        <f>K26*D26</f>
-        <v/>
-      </c>
-      <c r="M26" s="23">
-        <f>IF(I26=0,0,K26/I26)</f>
-        <v/>
-      </c>
-      <c r="N26" s="24">
-        <f>IF(G26=0,0,K26/G26)</f>
-        <v/>
-      </c>
-      <c r="O26" s="25">
-        <f>K26*F26</f>
-        <v/>
-      </c>
-      <c r="P26" s="26">
-        <f>K26*E26</f>
-        <v/>
-      </c>
-      <c r="Q26" s="27">
-        <f>L26/1000*J26</f>
-        <v/>
-      </c>
-      <c r="R26" s="28" t="inlineStr">
+      <c r="M26" s="24">
+        <f>L26*E26</f>
+        <v/>
+      </c>
+      <c r="N26" s="25">
+        <f>IF(D26="DOKME",0,IF(J26=0,0,L26/J26))</f>
+        <v/>
+      </c>
+      <c r="O26" s="26">
+        <f>IF(D26="DOKME",0,IF(H26=0,0,L26/H26))</f>
+        <v/>
+      </c>
+      <c r="P26" s="27">
+        <f>L26*G26</f>
+        <v/>
+      </c>
+      <c r="Q26" s="28">
+        <f>L26*F26</f>
+        <v/>
+      </c>
+      <c r="R26" s="29">
+        <f>IF(K26="",0,M26/1000*K26)</f>
+        <v/>
+      </c>
+      <c r="S26" s="30" t="inlineStr">
         <is>
           <t>PIZZA</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="36" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>PANDA ICE CREAM SPOON</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>WHITE</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>PALET</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="G27" s="21">
+        <f>E27*0.9/1000</f>
+        <v/>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" s="15">
+        <f>IF(OR(H27="",I27=""),0,H27*I27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="31" t="n"/>
+      <c r="L27" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="24">
+        <f>L27*E27</f>
+        <v/>
+      </c>
+      <c r="N27" s="25">
+        <f>IF(D27="DOKME",0,IF(J27=0,0,L27/J27))</f>
+        <v/>
+      </c>
+      <c r="O27" s="26">
+        <f>IF(D27="DOKME",0,IF(H27=0,0,L27/H27))</f>
+        <v/>
+      </c>
+      <c r="P27" s="27">
+        <f>L27*G27</f>
+        <v/>
+      </c>
+      <c r="Q27" s="28">
+        <f>L27*F27</f>
+        <v/>
+      </c>
+      <c r="R27" s="29">
+        <f>IF(K27="",0,M27/1000*K27)</f>
+        <v/>
+      </c>
+      <c r="S27" s="30" t="inlineStr">
+        <is>
+          <t>ICE CREAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>SHOT GLASS</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>TRANSPARENT</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>DOKME</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G28" s="21">
+        <f>E28*3.2/1000</f>
+        <v/>
+      </c>
+      <c r="H28" s="15" t="n"/>
+      <c r="I28" s="15" t="n"/>
+      <c r="J28" s="15">
+        <f>IF(OR(H28="",I28=""),0,H28*I28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="31" t="n"/>
+      <c r="L28" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="24">
+        <f>L28*E28</f>
+        <v/>
+      </c>
+      <c r="N28" s="25">
+        <f>IF(D28="DOKME",0,IF(J28=0,0,L28/J28))</f>
+        <v/>
+      </c>
+      <c r="O28" s="26">
+        <f>IF(D28="DOKME",0,IF(H28=0,0,L28/H28))</f>
+        <v/>
+      </c>
+      <c r="P28" s="27">
+        <f>L28*G28</f>
+        <v/>
+      </c>
+      <c r="Q28" s="28">
+        <f>L28*F28</f>
+        <v/>
+      </c>
+      <c r="R28" s="29">
+        <f>IF(K28="",0,M28/1000*K28)</f>
+        <v/>
+      </c>
+      <c r="S28" s="30" t="inlineStr">
+        <is>
+          <t>GLASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>95 MM FLAT ICE CREAM SPOON</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>COLORED (YELLOW/RED/BLACK)</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
+        <is>
+          <t>DOKME</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="G29" s="21">
+        <f>E29*1.25/1000</f>
+        <v/>
+      </c>
+      <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="15">
+        <f>IF(OR(H29="",I29=""),0,H29*I29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="31" t="n"/>
+      <c r="L29" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="24">
+        <f>L29*E29</f>
+        <v/>
+      </c>
+      <c r="N29" s="25">
+        <f>IF(D29="DOKME",0,IF(J29=0,0,L29/J29))</f>
+        <v/>
+      </c>
+      <c r="O29" s="26">
+        <f>IF(D29="DOKME",0,IF(H29=0,0,L29/H29))</f>
+        <v/>
+      </c>
+      <c r="P29" s="27">
+        <f>L29*G29</f>
+        <v/>
+      </c>
+      <c r="Q29" s="28">
+        <f>L29*F29</f>
+        <v/>
+      </c>
+      <c r="R29" s="29">
+        <f>IF(K29="",0,M29/1000*K29)</f>
+        <v/>
+      </c>
+      <c r="S29" s="30" t="inlineStr">
+        <is>
+          <t>ICE CREAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t>TOPLAM / GRAND TOTAL</t>
         </is>
       </c>
-      <c r="K27" s="37">
-        <f>SUM(K7:K26)</f>
-        <v/>
-      </c>
-      <c r="L27" s="37">
-        <f>SUM(L7:L26)</f>
-        <v/>
-      </c>
-      <c r="M27" s="38">
-        <f>SUM(M7:M26)</f>
-        <v/>
-      </c>
-      <c r="N27" s="39" t="n"/>
-      <c r="O27" s="40">
-        <f>SUM(O7:O26)</f>
-        <v/>
-      </c>
-      <c r="P27" s="41">
-        <f>SUM(P7:P26)</f>
-        <v/>
-      </c>
-      <c r="Q27" s="42">
-        <f>SUM(Q7:Q26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="43" t="inlineStr">
-        <is>
-          <t>*** SIPARIS (KOLI) sutununa yalnizca KOLI/SIRA (G sutunu) degerinin KATLARI girilebilir (1 palet sirasi = 1 tam sira; ornek Diamond Fork 12/sira -&gt; 12,24,36,48...). Yanlis katta Excel uyari verir. | PALET (esdeger) yarim paletleri de kapsar; gercek fiziksel palet ve TIR dolulugu icin 'PALET &amp; TIR OZETI' sayfasina bakin. | NAVIPACK standart TIR = 90 m3 (dolum hacme gore hesaplanir).</t>
+      <c r="L30" s="34">
+        <f>SUM(L7:L29)</f>
+        <v/>
+      </c>
+      <c r="M30" s="34">
+        <f>SUM(M7:M29)</f>
+        <v/>
+      </c>
+      <c r="N30" s="35">
+        <f>SUM(N7:N29)</f>
+        <v/>
+      </c>
+      <c r="O30" s="36" t="n"/>
+      <c r="P30" s="37">
+        <f>SUM(P7:P29)</f>
+        <v/>
+      </c>
+      <c r="Q30" s="38">
+        <f>SUM(Q7:Q29)</f>
+        <v/>
+      </c>
+      <c r="R30" s="39">
+        <f>SUM(R7:R29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="46" customHeight="1">
+      <c r="A31" s="40" t="inlineStr">
+        <is>
+          <t>*** PALET urunlerinde SIPARIS (KOLI), KOLI/SIRA (H) degerinin KATI olmalidir (1 palet sirasi = 1 tam sira; or. Diamond Fork 12/sira -&gt; 12,24,36,48...). DOKME (palet ustu dokme / bulk) urunlerinde her adet girilebilir, palet olusturmaz, sadece HACME katkida bulunur. Fiyati bilinmeyen ekstra urunlerde FIYAT/1000 hucresi saridir - elle giriniz.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A28:R28"/>
-    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="A1:E4"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A31:S31"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="N1:O1"/>
     <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K3:L3"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="K7:K26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="GECERSIZ ADET" error="Girdiginiz sayi KOLI/SIRA (G sutunu) degerinin tam kati degil. Lutfen tam sira olacak sekilde girin (or. 12'nin katlari)." promptTitle="SIPARIS (KOLI)" prompt="KOLI cinsinden girin. KOLI/SIRA (G) sutununun KATI olmalidir; boylece her palet sirasi tek urunle dolar ve yarim paletler duzgun birlesir.&#10;Ornek Diamond Fork (12/sira): 12,24,36,48,60..." type="custom">
-      <formula1>=AND(K7&gt;=0,MOD(K7,G7)=0)</formula1>
+  <dataValidations count="2">
+    <dataValidation sqref="L7:L29" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="GECERSIZ ADET" error="PALET urununde sayi KOLI/SIRA (H) katindan olmali (or. 12'nin katlari)." promptTitle="SIPARIS (KOLI)" prompt="PALET urun: KOLI cinsinden, KOLI/SIRA (H) KATI girin (or. 12,24,36,48).&#10;DOKME urun: istediginiz adet - palet olusturmaz, sadece hacme katilir." type="custom">
+      <formula1>=IF(D7="DOKME",L7&gt;=0,AND(L7&gt;=0,MOD(L7,H7)=0))</formula1>
+    </dataValidation>
+    <dataValidation sqref="D7:D29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"PALET,DOKME"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2426,7 +2774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2440,17 +2788,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="44" t="inlineStr">
-        <is>
-          <t>PALET &amp; TIR OZETI / PALLET &amp; TRUCK CONSOLIDATION</t>
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>PALET &amp; TIR OZETI / PALLET &amp; TRUCK SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="45" t="inlineStr">
-        <is>
-          <t>Yarim paletler ONCELIKLE ayni urun ailesi icinde birlestirilir (Diamond'lar Diamond'larla, Premium'lar Premium'larla, kasiklar kasiklarla). Cok az sayidaki kalanlar 'palet ustu dokme' olarak mevcut paletlerin ustune yuklenebilir. 'GERCEK PALET' = her ailenin palet-esdegerinin yukari yuvarlanmisi.</t>
+      <c r="A3" s="42" t="inlineStr">
+        <is>
+          <t>Yarim paletler ONCELIKLE ayni urun ailesi icinde birlestirilir (Diamond'lar Diamond'larla, Premium'lar Premium'larla). DOKME urunler palet olusturmaz; 'palet ustu dokme' olarak mevcut paletlerin ustune yuklenir, sadece hacme katkida bulunur. 'GERCEK PALET' = her ailenin palet-esdegerinin yukari yuvarlanmisi.</t>
         </is>
       </c>
     </row>
@@ -2465,33 +2813,33 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>DIAMOND CUTLERY</t>
         </is>
       </c>
-      <c r="B7" s="46">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I7,'SIPARIS - ORDER'!$K$7:$K$26)</f>
-        <v/>
-      </c>
-      <c r="C7" s="47">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I7,'SIPARIS - ORDER'!$M$7:$M$26)</f>
-        <v/>
-      </c>
-      <c r="D7" s="48">
+      <c r="B7" s="43">
+        <f>SUMIFS('SIPARIS - ORDER'!$L$7:$L$29,'SIPARIS - ORDER'!$S$7:$S$29,$I7,'SIPARIS - ORDER'!$D$7:$D$29,"PALET")</f>
+        <v/>
+      </c>
+      <c r="C7" s="44">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I7,'SIPARIS - ORDER'!$N$7:$N$29)</f>
+        <v/>
+      </c>
+      <c r="D7" s="45">
         <f>INT(C7)</f>
         <v/>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="46">
         <f>IF(C7=0,0,CEILING(C7,1))</f>
         <v/>
       </c>
-      <c r="F7" s="50">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I7,'SIPARIS - ORDER'!$O$7:$O$26)</f>
-        <v/>
-      </c>
-      <c r="G7" s="51">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I7,'SIPARIS - ORDER'!$P$7:$P$26)</f>
+      <c r="F7" s="47">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I7,'SIPARIS - ORDER'!$P$7:$P$29)</f>
+        <v/>
+      </c>
+      <c r="G7" s="48">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I7,'SIPARIS - ORDER'!$Q$7:$Q$29)</f>
         <v/>
       </c>
       <c r="I7" t="inlineStr">
@@ -2501,33 +2849,33 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>PREMIUM CUTLERY</t>
         </is>
       </c>
-      <c r="B8" s="46">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I8,'SIPARIS - ORDER'!$K$7:$K$26)</f>
-        <v/>
-      </c>
-      <c r="C8" s="47">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I8,'SIPARIS - ORDER'!$M$7:$M$26)</f>
-        <v/>
-      </c>
-      <c r="D8" s="48">
+      <c r="B8" s="43">
+        <f>SUMIFS('SIPARIS - ORDER'!$L$7:$L$29,'SIPARIS - ORDER'!$S$7:$S$29,$I8,'SIPARIS - ORDER'!$D$7:$D$29,"PALET")</f>
+        <v/>
+      </c>
+      <c r="C8" s="44">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I8,'SIPARIS - ORDER'!$N$7:$N$29)</f>
+        <v/>
+      </c>
+      <c r="D8" s="45">
         <f>INT(C8)</f>
         <v/>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="46">
         <f>IF(C8=0,0,CEILING(C8,1))</f>
         <v/>
       </c>
-      <c r="F8" s="50">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I8,'SIPARIS - ORDER'!$O$7:$O$26)</f>
-        <v/>
-      </c>
-      <c r="G8" s="51">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I8,'SIPARIS - ORDER'!$P$7:$P$26)</f>
+      <c r="F8" s="47">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I8,'SIPARIS - ORDER'!$P$7:$P$29)</f>
+        <v/>
+      </c>
+      <c r="G8" s="48">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I8,'SIPARIS - ORDER'!$Q$7:$Q$29)</f>
         <v/>
       </c>
       <c r="I8" t="inlineStr">
@@ -2537,33 +2885,33 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>SMART FORK</t>
         </is>
       </c>
-      <c r="B9" s="46">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I9,'SIPARIS - ORDER'!$K$7:$K$26)</f>
-        <v/>
-      </c>
-      <c r="C9" s="47">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I9,'SIPARIS - ORDER'!$M$7:$M$26)</f>
-        <v/>
-      </c>
-      <c r="D9" s="48">
+      <c r="B9" s="43">
+        <f>SUMIFS('SIPARIS - ORDER'!$L$7:$L$29,'SIPARIS - ORDER'!$S$7:$S$29,$I9,'SIPARIS - ORDER'!$D$7:$D$29,"PALET")</f>
+        <v/>
+      </c>
+      <c r="C9" s="44">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I9,'SIPARIS - ORDER'!$N$7:$N$29)</f>
+        <v/>
+      </c>
+      <c r="D9" s="45">
         <f>INT(C9)</f>
         <v/>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="46">
         <f>IF(C9=0,0,CEILING(C9,1))</f>
         <v/>
       </c>
-      <c r="F9" s="50">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I9,'SIPARIS - ORDER'!$O$7:$O$26)</f>
-        <v/>
-      </c>
-      <c r="G9" s="51">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I9,'SIPARIS - ORDER'!$P$7:$P$26)</f>
+      <c r="F9" s="47">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I9,'SIPARIS - ORDER'!$P$7:$P$29)</f>
+        <v/>
+      </c>
+      <c r="G9" s="48">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I9,'SIPARIS - ORDER'!$Q$7:$Q$29)</f>
         <v/>
       </c>
       <c r="I9" t="inlineStr">
@@ -2573,33 +2921,33 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>ICE CREAM SPOON</t>
         </is>
       </c>
-      <c r="B10" s="46">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I10,'SIPARIS - ORDER'!$K$7:$K$26)</f>
-        <v/>
-      </c>
-      <c r="C10" s="47">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I10,'SIPARIS - ORDER'!$M$7:$M$26)</f>
-        <v/>
-      </c>
-      <c r="D10" s="48">
+      <c r="B10" s="43">
+        <f>SUMIFS('SIPARIS - ORDER'!$L$7:$L$29,'SIPARIS - ORDER'!$S$7:$S$29,$I10,'SIPARIS - ORDER'!$D$7:$D$29,"PALET")</f>
+        <v/>
+      </c>
+      <c r="C10" s="44">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I10,'SIPARIS - ORDER'!$N$7:$N$29)</f>
+        <v/>
+      </c>
+      <c r="D10" s="45">
         <f>INT(C10)</f>
         <v/>
       </c>
-      <c r="E10" s="49">
+      <c r="E10" s="46">
         <f>IF(C10=0,0,CEILING(C10,1))</f>
         <v/>
       </c>
-      <c r="F10" s="50">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I10,'SIPARIS - ORDER'!$O$7:$O$26)</f>
-        <v/>
-      </c>
-      <c r="G10" s="51">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I10,'SIPARIS - ORDER'!$P$7:$P$26)</f>
+      <c r="F10" s="47">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I10,'SIPARIS - ORDER'!$P$7:$P$29)</f>
+        <v/>
+      </c>
+      <c r="G10" s="48">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I10,'SIPARIS - ORDER'!$Q$7:$Q$29)</f>
         <v/>
       </c>
       <c r="I10" t="inlineStr">
@@ -2609,33 +2957,33 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>GLASSES / CUPS</t>
         </is>
       </c>
-      <c r="B11" s="46">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I11,'SIPARIS - ORDER'!$K$7:$K$26)</f>
-        <v/>
-      </c>
-      <c r="C11" s="47">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I11,'SIPARIS - ORDER'!$M$7:$M$26)</f>
-        <v/>
-      </c>
-      <c r="D11" s="48">
+      <c r="B11" s="43">
+        <f>SUMIFS('SIPARIS - ORDER'!$L$7:$L$29,'SIPARIS - ORDER'!$S$7:$S$29,$I11,'SIPARIS - ORDER'!$D$7:$D$29,"PALET")</f>
+        <v/>
+      </c>
+      <c r="C11" s="44">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I11,'SIPARIS - ORDER'!$N$7:$N$29)</f>
+        <v/>
+      </c>
+      <c r="D11" s="45">
         <f>INT(C11)</f>
         <v/>
       </c>
-      <c r="E11" s="49">
+      <c r="E11" s="46">
         <f>IF(C11=0,0,CEILING(C11,1))</f>
         <v/>
       </c>
-      <c r="F11" s="50">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I11,'SIPARIS - ORDER'!$O$7:$O$26)</f>
-        <v/>
-      </c>
-      <c r="G11" s="51">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I11,'SIPARIS - ORDER'!$P$7:$P$26)</f>
+      <c r="F11" s="47">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I11,'SIPARIS - ORDER'!$P$7:$P$29)</f>
+        <v/>
+      </c>
+      <c r="G11" s="48">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I11,'SIPARIS - ORDER'!$Q$7:$Q$29)</f>
         <v/>
       </c>
       <c r="I11" t="inlineStr">
@@ -2645,33 +2993,33 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>PIZZA TRIPOD</t>
         </is>
       </c>
-      <c r="B12" s="46">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I12,'SIPARIS - ORDER'!$K$7:$K$26)</f>
-        <v/>
-      </c>
-      <c r="C12" s="47">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I12,'SIPARIS - ORDER'!$M$7:$M$26)</f>
-        <v/>
-      </c>
-      <c r="D12" s="48">
+      <c r="B12" s="43">
+        <f>SUMIFS('SIPARIS - ORDER'!$L$7:$L$29,'SIPARIS - ORDER'!$S$7:$S$29,$I12,'SIPARIS - ORDER'!$D$7:$D$29,"PALET")</f>
+        <v/>
+      </c>
+      <c r="C12" s="44">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I12,'SIPARIS - ORDER'!$N$7:$N$29)</f>
+        <v/>
+      </c>
+      <c r="D12" s="45">
         <f>INT(C12)</f>
         <v/>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="46">
         <f>IF(C12=0,0,CEILING(C12,1))</f>
         <v/>
       </c>
-      <c r="F12" s="50">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I12,'SIPARIS - ORDER'!$O$7:$O$26)</f>
-        <v/>
-      </c>
-      <c r="G12" s="51">
-        <f>SUMIF('SIPARIS - ORDER'!$R$7:$R$26,$I12,'SIPARIS - ORDER'!$P$7:$P$26)</f>
+      <c r="F12" s="47">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I12,'SIPARIS - ORDER'!$P$7:$P$29)</f>
+        <v/>
+      </c>
+      <c r="G12" s="48">
+        <f>SUMIF('SIPARIS - ORDER'!$S$7:$S$29,$I12,'SIPARIS - ORDER'!$Q$7:$Q$29)</f>
         <v/>
       </c>
       <c r="I12" t="inlineStr">
@@ -2681,139 +3029,167 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="52" t="inlineStr">
+      <c r="A13" s="49" t="inlineStr">
+        <is>
+          <t>PALET USTU DOKME / BULK</t>
+        </is>
+      </c>
+      <c r="B13" s="50">
+        <f>SUMIF('SIPARIS - ORDER'!$D$7:$D$29,"DOKME",'SIPARIS - ORDER'!$L$7:$L$29)</f>
+        <v/>
+      </c>
+      <c r="C13" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="53">
+        <f>SUMIF('SIPARIS - ORDER'!$D$7:$D$29,"DOKME",'SIPARIS - ORDER'!$P$7:$P$29)</f>
+        <v/>
+      </c>
+      <c r="G13" s="54">
+        <f>SUMIF('SIPARIS - ORDER'!$D$7:$D$29,"DOKME",'SIPARIS - ORDER'!$Q$7:$Q$29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="55" t="inlineStr">
         <is>
           <t>TOPLAM / GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="37">
-        <f>SUM(B7:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="38">
-        <f>SUM(C7:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="53">
-        <f>SUM(D7:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="53">
-        <f>SUM(E7:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="40">
-        <f>SUM(F7:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="41">
-        <f>SUM(G7:G12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="54" t="inlineStr">
+      <c r="B14" s="34">
+        <f>SUM(B7:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="35">
+        <f>SUM(C7:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="56">
+        <f>SUM(D7:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="56">
+        <f>SUM(E7:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="37">
+        <f>SUM(F7:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="38">
+        <f>SUM(G7:G13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="57" t="inlineStr">
         <is>
           <t>TIR / TRUCK YUKLEME (hacme gore / by volume)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="55" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="58" t="inlineStr">
         <is>
           <t>TIR KAPASITESI (m3):</t>
         </is>
       </c>
-      <c r="B16" s="56" t="n"/>
-      <c r="C16" s="56" t="n"/>
-      <c r="D16" s="56" t="n"/>
-      <c r="E16" s="57">
+      <c r="B17" s="59" t="n"/>
+      <c r="C17" s="59" t="n"/>
+      <c r="D17" s="59" t="n"/>
+      <c r="E17" s="60">
         <f>'SIPARIS - ORDER'!$G$3</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="55" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="58" t="inlineStr">
         <is>
           <t>TOPLAM SIPARIS HACMI (m3):</t>
         </is>
       </c>
-      <c r="B17" s="56" t="n"/>
-      <c r="C17" s="56" t="n"/>
-      <c r="D17" s="56" t="n"/>
-      <c r="E17" s="57">
-        <f>G13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="55" t="inlineStr">
+      <c r="B18" s="59" t="n"/>
+      <c r="C18" s="59" t="n"/>
+      <c r="D18" s="59" t="n"/>
+      <c r="E18" s="60">
+        <f>G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="58" t="inlineStr">
         <is>
           <t>TIR DOLULUK ORANI:</t>
         </is>
       </c>
-      <c r="B18" s="56" t="n"/>
-      <c r="C18" s="56" t="n"/>
-      <c r="D18" s="56" t="n"/>
-      <c r="E18" s="58">
-        <f>IF(E16=0,0,G13/E16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="55" t="inlineStr">
+      <c r="B19" s="59" t="n"/>
+      <c r="C19" s="59" t="n"/>
+      <c r="D19" s="59" t="n"/>
+      <c r="E19" s="61">
+        <f>IF(E17=0,0,G14/E17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="58" t="inlineStr">
         <is>
           <t>GEREKEN TIR ADEDI:</t>
         </is>
       </c>
-      <c r="B19" s="56" t="n"/>
-      <c r="C19" s="56" t="n"/>
-      <c r="D19" s="56" t="n"/>
-      <c r="E19" s="59">
-        <f>IF(E16=0,0,CEILING(G13/E16,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="55" t="inlineStr">
+      <c r="B20" s="59" t="n"/>
+      <c r="C20" s="59" t="n"/>
+      <c r="D20" s="59" t="n"/>
+      <c r="E20" s="62">
+        <f>IF(E17=0,0,CEILING(G14/E17,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="58" t="inlineStr">
         <is>
           <t>SON TIR'DA BOS HACIM (m3):</t>
         </is>
       </c>
-      <c r="B20" s="56" t="n"/>
-      <c r="C20" s="56" t="n"/>
-      <c r="D20" s="56" t="n"/>
-      <c r="E20" s="57">
-        <f>IF(E16=0,0,E19*E16-G13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="60" t="inlineStr">
-        <is>
-          <t>NOT: TIR dolulugu HACME gore hesaplanir (NAVIPACK standart TIR = 90 m3; cift dorse = 120 m3 - ust taraftaki kapasiteyi degistirebilirsiniz). Farkli aileler yalnizca koli yukseklikleri uyumluysa ayni palette birlestirilebilir; bu durumda palet sayisi daha da dusebilir. Nihai istifleme fabrikada fiziksel olarak teyit edilir. Her palet sirasi TEK urunle dolmalidir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
+      <c r="B21" s="59" t="n"/>
+      <c r="C21" s="59" t="n"/>
+      <c r="D21" s="59" t="n"/>
+      <c r="E21" s="60">
+        <f>IF(E17=0,0,E20*E17-G14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="63" t="inlineStr">
+        <is>
+          <t>NOT: TIR dolulugu HACME gore hesaplanir (NAVIPACK standart = 90 m3; cift dorse = 120 m3). DOKME urunlerin hacmi toplama dahildir ancak palet sayisina eklenmez (mevcut paletlerin ustune yuklenir). Farkli aileler yalnizca koli yukseklikleri uyumluysa ayni palette birlestirilebilir. Nihai istifleme fabrikada teyit edilir.</t>
+        </is>
+      </c>
+    </row>
     <row r="24"/>
     <row r="25"/>
+    <row r="26"/>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A22:G25"/>
+    <mergeCell ref="A23:G26"/>
     <mergeCell ref="A3:G4"/>
     <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="E17:G17"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="E18:G18"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E21:G21"/>
     <mergeCell ref="E20:G20"/>
-    <mergeCell ref="E16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2825,7 +3201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B43"/>
+  <dimension ref="B1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2833,271 +3209,215 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="B1" s="61" t="inlineStr">
-        <is>
-          <t>NAVIPACK - SIPARIS &amp; HACIM HESAPLAMA / ORDER &amp; VOLUME CALCULATOR (v2)</t>
+      <c r="B1" s="64" t="inlineStr">
+        <is>
+          <t>NAVIPACK - SIPARIS &amp; HACIM HESAPLAMA / ORDER &amp; VOLUME CALCULATOR (v3)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="62" t="inlineStr"/>
+      <c r="B2" s="65" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="B3" s="63" t="inlineStr">
+      <c r="B3" s="66" t="inlineStr">
         <is>
           <t>NASIL KULLANILIR / HOW TO USE</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="62" t="inlineStr">
-        <is>
-          <t>1) 'SIPARIS - ORDER' sayfasinda SADECE sari 'SIPARIS (KOLI)' sutununu (K) doldurun.</t>
+      <c r="B4" s="65" t="inlineStr">
+        <is>
+          <t>1) 'SIPARIS - ORDER' sayfasinda sari 'SIPARIS (KOLI)' sutununu (L) doldurun.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="62" t="inlineStr">
+      <c r="B5" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">   Ustten Musteri, Tarih ve TIR Kapasitesini (varsayilan 90 m3) girin.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="62" t="inlineStr">
-        <is>
-          <t>2) Ust bantta anlik KPI'lar: Toplam Hacim, TIR Doluluk %, Gereken TIR adedi, Toplam Tutar.</t>
+      <c r="B6" s="65" t="inlineStr">
+        <is>
+          <t>2) Ust bantta KPI: Toplam Hacim, TIR Doluluk %, Gereken TIR adedi, Toplam Tutar.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="62" t="inlineStr">
-        <is>
-          <t>3) 'PALET &amp; TIR OZETI' sayfasi paletleri aile bazinda birlestirir ve TIR dolulugunu gosterir.</t>
+      <c r="B7" s="65" t="inlineStr">
+        <is>
+          <t>3) 'PALET &amp; TIR OZETI' paletleri aile bazinda birlestirir + TIR dolulugunu gosterir.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="62" t="inlineStr"/>
+      <c r="B8" s="65" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="B9" s="63" t="inlineStr">
-        <is>
-          <t>NEDEN KOLI/SIRA'NIN KATLARI? / WHY MULTIPLES OF BOX-PER-LAYER?</t>
+      <c r="B9" s="66" t="inlineStr">
+        <is>
+          <t>YUKLEME TIPI: PALET vs DOKME</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="62" t="inlineStr">
-        <is>
-          <t>Musteri her zaman paletli (100x120 cm) yukleme yapar. Bir palet sirasina FARKLI urun dizilirse koli</t>
+      <c r="B10" s="65" t="inlineStr">
+        <is>
+          <t>PALET = paletli yuklenir. SIPARIS, KOLI/SIRA (H) degerinin KATI olmalidir (tam sira).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="62" t="inlineStr">
-        <is>
-          <t>yukseklikleri farkli olur ve palet dengesiz yukselir. Bu yuzden her sira TEK urunle DOLU olmalidir;</t>
+      <c r="B11" s="65" t="inlineStr">
+        <is>
+          <t>DOKME = 'palet ustu dokme' / bulk. Serbest adet girilir; palet olusturmaz, sadece HACME</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="62" t="inlineStr">
-        <is>
-          <t>siparis daima tam sira (KOLI/SIRA'nin kati) girilir. Boylece kalan yarim paletler duzgun birlesir.</t>
+      <c r="B12" s="65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   katkida bulunur (mevcut paletlerin ustune / TIR bosluguna yuklenir). Or. 95mm Flat Kasik, Shot Glass.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="62" t="inlineStr">
-        <is>
-          <t>Ornek: Diamond Fork 1 sirada 12 koli -&gt; 12, 24, 36, 48 ... (45 yerine 48).</t>
-        </is>
-      </c>
+      <c r="B13" s="65" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="B14" s="62" t="inlineStr"/>
+      <c r="B14" s="66" t="inlineStr">
+        <is>
+          <t>NEDEN KOLI/SIRA KATLARI?</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="63" t="inlineStr">
-        <is>
-          <t>ADET -&gt; KOLI / UNITS -&gt; BOXES</t>
+      <c r="B15" s="65" t="inlineStr">
+        <is>
+          <t>Bir palet sirasina farkli urun dizilirse koli yukseklikleri farkli olur, palet dengesiz yukselir.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="62" t="inlineStr">
-        <is>
-          <t>Siparis cogu zaman ADET konusulur. 1 kolideki adet 'ADET/KOLI' sutunundadir (or. Diamond 2.000).</t>
+      <c r="B16" s="65" t="inlineStr">
+        <is>
+          <t>Bu yuzden her sira TEK urunle DOLU olmali; siparis tam sira (KOLI/SIRA kati) girilir.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="62" t="inlineStr">
-        <is>
-          <t>600.000 adet Diamond Fork / 2.000 = 300 koli. 1 palet = 120 koli -&gt; 300 koli = 2 tam palet + yarim palet.</t>
+      <c r="B17" s="65" t="inlineStr">
+        <is>
+          <t>Ornek: Diamond Fork 12/sira -&gt; 12, 24, 36, 48 ... (45 yerine 48).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="62" t="inlineStr"/>
+      <c r="B18" s="65" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="63" t="inlineStr">
-        <is>
-          <t>YARIM PALET BIRLESTIRME &amp; PALET USTU DOKME</t>
+      <c r="B19" s="66" t="inlineStr">
+        <is>
+          <t>TIR / TRUCK</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="62" t="inlineStr">
-        <is>
-          <t>Oncelik ayni aile: Diamond'lar Diamond'larla, Premium'lar Premium'larla, kasiklar kasiklarla.</t>
+      <c r="B20" s="65" t="inlineStr">
+        <is>
+          <t>NAVIPACK standart TIR = 90 m3 (dolum HACME gore). Cift dorse TIR = 120 m3.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="62" t="inlineStr">
-        <is>
-          <t>Cok az sayidaki kalan koliler (or. birkac koli Wavy/Shot Glass) 'palet ustu dokme' olarak mevcut</t>
+      <c r="B21" s="65" t="inlineStr">
+        <is>
+          <t>FERPROM gibi TAMAMEN dokme yukleyen firmalarda palet yoktur; ayri 'FERPROM Dokme' dosyasina bakin.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="62" t="inlineStr">
-        <is>
-          <t>paletlerin ustune yerlestirilebilir. 'PALET &amp; TIR OZETI' bu birlestirmeyi ozetler.</t>
-        </is>
-      </c>
+      <c r="B22" s="65" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="B23" s="62" t="inlineStr"/>
+      <c r="B23" s="66" t="inlineStr">
+        <is>
+          <t>EKSTRA URUNLER (teklifte fiyat yok)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="63" t="inlineStr">
-        <is>
-          <t>TIR / TRUCK</t>
+      <c r="B24" s="65" t="inlineStr">
+        <is>
+          <t>PANDA / 95mm FLAT / SHOT GLASS: NAVIPACK volume tablosunda var, fiyat teklifinde yok.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="62" t="inlineStr">
-        <is>
-          <t>NAVIPACK standart TIR = 90 m3 (dolum HACME gore). Cift dorse TIR = 120 m3.</t>
+      <c r="B25" s="65" t="inlineStr">
+        <is>
+          <t>Bunlarin FIYAT/1000 hucresi sari - siparise gore elle giriniz.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="62" t="inlineStr">
-        <is>
-          <t>Gereken TIR = Toplam Hacim / Kapasite (yukari yuvarlanir). FERPROM gibi tamamen dokme yukleyen</t>
-        </is>
-      </c>
+      <c r="B26" s="65" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="B27" s="62" t="inlineStr">
-        <is>
-          <t>firmalarda palet yoktur; sadece toplam hacim TIR'a sigacak sekilde hesaplanir.</t>
+      <c r="B27" s="66" t="inlineStr">
+        <is>
+          <t>HESAPLAMALAR</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="62" t="inlineStr"/>
+      <c r="B28" s="65" t="inlineStr">
+        <is>
+          <t>SIPARIS (ADET) = Koli x Adet/Koli | PALET (esdeger)=Koli/(Koli/Palet) | TAM SIRA=Koli/(Koli/Sira)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="B29" s="63" t="inlineStr">
-        <is>
-          <t>HESAPLAMALAR / FORMULAS</t>
+      <c r="B29" s="65" t="inlineStr">
+        <is>
+          <t>NET AGIRLIK=Koli x (Adet/Koli x gr /1000) | HACIM=Koli x Koli Hacmi | TUTAR=(Adet/1000) x Fiyat</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="62" t="inlineStr">
-        <is>
-          <t>SIPARIS (ADET)  = Siparis Koli x Adet/Koli</t>
-        </is>
-      </c>
+      <c r="B30" s="65" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="B31" s="62" t="inlineStr">
-        <is>
-          <t>PALET (esdeger) = Siparis Koli / (Koli/Palet)     [Koli/Palet = Koli/Sira x Sira/Palet]</t>
+      <c r="B31" s="66" t="inlineStr">
+        <is>
+          <t>RENK KODLARI</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="62" t="inlineStr">
-        <is>
-          <t>TAM SIRA        = Siparis Koli / (Koli/Sira)</t>
+      <c r="B32" s="65" t="inlineStr">
+        <is>
+          <t>Sari=veri girisi | Yesil=otomatik sonuc | Turuncu=DOKME/bulk | Gri=referans | Mavi=KPI.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="62" t="inlineStr">
-        <is>
-          <t>NET AGIRLIK kg  = Siparis Koli x (Adet/Koli x urun agirligi gr / 1000)</t>
-        </is>
-      </c>
+      <c r="B33" s="65" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="B34" s="62" t="inlineStr">
-        <is>
-          <t>HACIM m3        = Siparis Koli x Koli Hacmi m3</t>
+      <c r="B34" s="66" t="inlineStr">
+        <is>
+          <t>KAYNAKLAR</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="62" t="inlineStr">
-        <is>
-          <t>TUTAR USD       = (Siparis Adet / 1000) x Birim Fiyat</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="62" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="63" t="inlineStr">
-        <is>
-          <t>RENK KODLARI / LEGEND</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="62" t="inlineStr">
-        <is>
-          <t>Sari = veri girisi (siz doldurun) | Yesil = otomatik sonuc | Gri = referans (aile) | Mavi bant = KPI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="62" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="63" t="inlineStr">
-        <is>
-          <t>KAYNAKLAR / SOURCES</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="62" t="inlineStr">
-        <is>
-          <t>Urun listesi, fiyatlar ve palet dizilimleri: NAVIPACK Price Offer 20.06.2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="62" t="inlineStr">
-        <is>
-          <t>Palet dogrulama &amp; palet ustu dokme: NAVIPACK Volume Calculation 07.07.2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="62" t="inlineStr">
-        <is>
-          <t>TIR kapasiteleri: NAVIPACK standart 90 m3, FERPROM cift dorse 120 m3.</t>
+      <c r="B35" s="65" t="inlineStr">
+        <is>
+          <t>NAVIPACK Price Offer 20.06.2026 + Volume Calculation 07.07.2026. TIR: standart 90 m3.</t>
         </is>
       </c>
     </row>
